--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Discovery_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Discovery_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R7ec2c9bd0e6f4182"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rc1f30054d0124904"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Re282793db2e04a72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R296faf55b14a40c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Ra9b5d61730184296"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R5599585815d748de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R4fb7b56bb62e4132"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Raba61e2736e14433"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Re21c7d683e9d48ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rc79b2903ae134e2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R82fb6ab5f8394d39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R89b84eb59f064bb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rf505e1be74a94c71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R8577a179aa9c4018"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R70a04d62eaf5452a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R46b3b9afe5494c09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R01b220489d1a4bba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R3f1b309a21f544c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R26ed565644494d45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R4e42e4473d184823"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rfda98e711f0347f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R3ed3746bca644a00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rb8ff26954da9472f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R04300a3b04034256"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R739dce4abcbe4eba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Re72ae43066694e77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R823db565bd0c4a1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R4907c97cc0fb47bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R4d96954f106f4215"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rba153eaaf9114c5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R4cd9d9d31a3145f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R4c9765fe883e4fe3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R8af493cf5b8340a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rd5d7885b06184a4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R2b0665e4f2274bad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rd2118e4ac0994560"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R4b5d9de797214e9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rbdbb0a596ea5452e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rb19ed8969c354ca3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rb7482e2d3e314d2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R94a1f50db488411b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R0c3caf3c0c3d4cea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rfe381aaa73a443ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Re33e27b4facf4893"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R7385e9f07ddc4891"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R23cef640e0e04f29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R1f5bc07683864681"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rff3920a5da24468e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R7d61fa068b7c4d37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R70558b526798494a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R973d95f36cfb4bd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rbb1c7dfc18a6447a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rb6b6094458494ee4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R877a782825204dbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Ra53447bf3ca2446d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R1c8e0392ed804be7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -230,12 +230,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -2156,7 +2150,7 @@
       <x:c r="A5" s="2" t="str">
         <x:v>Fiches suivies</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>160</x:v>
       </x:c>
@@ -2164,7 +2158,7 @@
       <x:c r="D5" s="2" t="str">
         <x:v>Intégrés</x:v>
       </x:c>
-      <x:c r="E5" s="33" t="n">
+      <x:c r="E5" s="31" t="n">
         <x:f>SUM(E10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2172,7 +2166,7 @@
       <x:c r="G5" s="2" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="H5" s="33" t="n">
+      <x:c r="H5" s="31" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>28</x:v>
       </x:c>
@@ -2180,7 +2174,7 @@
       <x:c r="J5" s="2" t="str">
         <x:v>Extrapolations</x:v>
       </x:c>
-      <x:c r="K5" s="33" t="n">
+      <x:c r="K5" s="31" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>129</x:v>
       </x:c>
@@ -2203,7 +2197,7 @@
       <x:c r="M6" s="2"/>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="34" t="str">
+      <x:c r="A7" s="32" t="str">
         <x:v>Défini = spécification. Établi = référence documentée. Les colonnes d’adaptation restent des propositions.</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
@@ -2235,95 +2229,95 @@
       <x:c r="M8" s="2"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="30" t="str">
+      <x:c r="A9" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="29" t="str">
         <x:v>Total</x:v>
       </x:c>
-      <x:c r="C9" s="31" t="str">
+      <x:c r="C9" s="29" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="str">
+      <x:c r="D9" s="29" t="str">
         <x:v>Prototype</x:v>
       </x:c>
-      <x:c r="E9" s="31" t="str">
+      <x:c r="E9" s="29" t="str">
         <x:v>Intégré</x:v>
       </x:c>
-      <x:c r="F9" s="31" t="str">
+      <x:c r="F9" s="29" t="str">
         <x:v>Validé</x:v>
       </x:c>
-      <x:c r="G9" s="31" t="str">
+      <x:c r="G9" s="29" t="str">
         <x:v>Établi</x:v>
       </x:c>
-      <x:c r="H9" s="31" t="str">
+      <x:c r="H9" s="29" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="I9" s="31" t="str">
+      <x:c r="I9" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="str">
+      <x:c r="J9" s="29" t="str">
         <x:v>Coupé attesté</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="str">
+      <x:c r="K9" s="29" t="str">
         <x:v>Concept abandonné</x:v>
       </x:c>
-      <x:c r="L9" s="31" t="str">
+      <x:c r="L9" s="29" t="str">
         <x:v>Allégation écartée</x:v>
       </x:c>
-      <x:c r="M9" s="32" t="str">
+      <x:c r="M9" s="30" t="str">
         <x:v>Priorité P0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="35" t="str">
+      <x:c r="A10" s="33" t="str">
         <x:v>Personnages</x:v>
       </x:c>
-      <x:c r="B10" s="39" t="n">
+      <x:c r="B10" s="37" t="n">
         <x:f>COUNTA('Personnages'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C10" s="39" t="n">
+      <x:c r="C10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D10" s="39" t="n">
+      <x:c r="D10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="39" t="n">
+      <x:c r="E10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="39" t="n">
+      <x:c r="F10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="39" t="n">
+      <x:c r="G10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H10" s="39" t="n">
+      <x:c r="H10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I10" s="39" t="n">
+      <x:c r="I10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="J10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="39" t="n">
+      <x:c r="K10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="39" t="n">
+      <x:c r="L10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="n">
+      <x:c r="M10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2332,104 +2326,104 @@
       <x:c r="A11" s="2" t="str">
         <x:v>PNJ</x:v>
       </x:c>
-      <x:c r="B11" s="40" t="n">
+      <x:c r="B11" s="38" t="n">
         <x:f>COUNTA('PNJ'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C11" s="40" t="n">
+      <x:c r="C11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D11" s="40" t="n">
+      <x:c r="D11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="40" t="n">
+      <x:c r="E11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F11" s="40" t="n">
+      <x:c r="F11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G11" s="40" t="n">
+      <x:c r="G11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H11" s="40" t="n">
+      <x:c r="H11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I11" s="40" t="n">
+      <x:c r="I11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="40" t="n">
+      <x:c r="K11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L11" s="40" t="n">
+      <x:c r="L11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M11" s="40" t="n">
+      <x:c r="M11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="35" t="str">
+      <x:c r="A12" s="33" t="str">
         <x:v>Espèces et factions</x:v>
       </x:c>
-      <x:c r="B12" s="39" t="n">
+      <x:c r="B12" s="37" t="n">
         <x:f>COUNTA('Especes_factions'!$A$7:$A$18)</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C12" s="39" t="n">
+      <x:c r="C12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$18,"Défini")</x:f>
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D12" s="39" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$18,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$18,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="39" t="n">
+      <x:c r="F12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$18,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="39" t="n">
+      <x:c r="G12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$18,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H12" s="39" t="n">
+      <x:c r="H12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$18,"À vérifier")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I12" s="39" t="n">
+      <x:c r="I12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$18,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="39" t="n">
+      <x:c r="J12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$18,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="39" t="n">
+      <x:c r="K12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$18,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="39" t="n">
+      <x:c r="L12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$18,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="n">
+      <x:c r="M12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$E$7:$E$18,"P0")</x:f>
         <x:v>4</x:v>
       </x:c>
@@ -2438,104 +2432,104 @@
       <x:c r="A13" s="2" t="str">
         <x:v>Mondes</x:v>
       </x:c>
-      <x:c r="B13" s="40" t="n">
+      <x:c r="B13" s="38" t="n">
         <x:f>COUNTA('Mondes'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C13" s="40" t="n">
+      <x:c r="C13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D13" s="40" t="n">
+      <x:c r="D13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E13" s="40" t="n">
+      <x:c r="E13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="40" t="n">
+      <x:c r="F13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="40" t="n">
+      <x:c r="G13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H13" s="40" t="n">
+      <x:c r="H13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I13" s="40" t="n">
+      <x:c r="I13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J13" s="40" t="n">
+      <x:c r="J13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="40" t="n">
+      <x:c r="K13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L13" s="40" t="n">
+      <x:c r="L13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="40" t="n">
+      <x:c r="M13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$E$7:$E$11,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="35" t="str">
+      <x:c r="A14" s="33" t="str">
         <x:v>Zones</x:v>
       </x:c>
-      <x:c r="B14" s="39" t="n">
+      <x:c r="B14" s="37" t="n">
         <x:f>COUNTA('Zones'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C14" s="39" t="n">
+      <x:c r="C14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D14" s="39" t="n">
+      <x:c r="D14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="39" t="n">
+      <x:c r="E14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="39" t="n">
+      <x:c r="F14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="39" t="n">
+      <x:c r="G14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H14" s="39" t="n">
+      <x:c r="H14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I14" s="39" t="n">
+      <x:c r="I14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J14" s="39" t="n">
+      <x:c r="J14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="39" t="n">
+      <x:c r="K14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="39" t="n">
+      <x:c r="L14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="39" t="n">
+      <x:c r="M14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$E$7:$E$11,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2544,104 +2538,104 @@
       <x:c r="A15" s="2" t="str">
         <x:v>Liaisons</x:v>
       </x:c>
-      <x:c r="B15" s="40" t="n">
+      <x:c r="B15" s="38" t="n">
         <x:f>COUNTA('Liaisons'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C15" s="40" t="n">
+      <x:c r="C15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D15" s="40" t="n">
+      <x:c r="D15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="40" t="n">
+      <x:c r="E15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="40" t="n">
+      <x:c r="F15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="40" t="n">
+      <x:c r="G15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H15" s="40" t="n">
+      <x:c r="H15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I15" s="40" t="n">
+      <x:c r="I15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J15" s="40" t="n">
+      <x:c r="J15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="40" t="n">
+      <x:c r="K15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="40" t="n">
+      <x:c r="L15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M15" s="40" t="n">
+      <x:c r="M15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$E$7:$E$11,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="35" t="str">
+      <x:c r="A16" s="33" t="str">
         <x:v>Décors</x:v>
       </x:c>
-      <x:c r="B16" s="39" t="n">
+      <x:c r="B16" s="37" t="n">
         <x:f>COUNTA('Decors'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C16" s="39" t="n">
+      <x:c r="C16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D16" s="39" t="n">
+      <x:c r="D16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="39" t="n">
+      <x:c r="E16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="39" t="n">
+      <x:c r="F16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="39" t="n">
+      <x:c r="G16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H16" s="39" t="n">
+      <x:c r="H16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I16" s="39" t="n">
+      <x:c r="I16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J16" s="39" t="n">
+      <x:c r="J16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K16" s="39" t="n">
+      <x:c r="K16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L16" s="39" t="n">
+      <x:c r="L16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M16" s="39" t="n">
+      <x:c r="M16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$E$7:$E$11,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2650,104 +2644,104 @@
       <x:c r="A17" s="2" t="str">
         <x:v>Props</x:v>
       </x:c>
-      <x:c r="B17" s="40" t="n">
+      <x:c r="B17" s="38" t="n">
         <x:f>COUNTA('Props'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C17" s="40" t="n">
+      <x:c r="C17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D17" s="40" t="n">
+      <x:c r="D17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="40" t="n">
+      <x:c r="E17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F17" s="40" t="n">
+      <x:c r="F17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="40" t="n">
+      <x:c r="G17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H17" s="40" t="n">
+      <x:c r="H17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I17" s="40" t="n">
+      <x:c r="I17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J17" s="40" t="n">
+      <x:c r="J17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="40" t="n">
+      <x:c r="K17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="40" t="n">
+      <x:c r="L17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="40" t="n">
+      <x:c r="M17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="35" t="str">
+      <x:c r="A18" s="33" t="str">
         <x:v>Ennemis et boss</x:v>
       </x:c>
-      <x:c r="B18" s="39" t="n">
+      <x:c r="B18" s="37" t="n">
         <x:f>COUNTA('Ennemis_boss'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C18" s="39" t="n">
+      <x:c r="C18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D18" s="39" t="n">
+      <x:c r="D18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="39" t="n">
+      <x:c r="E18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="39" t="n">
+      <x:c r="F18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="39" t="n">
+      <x:c r="G18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H18" s="39" t="n">
+      <x:c r="H18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I18" s="39" t="n">
+      <x:c r="I18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J18" s="39" t="n">
+      <x:c r="J18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="39" t="n">
+      <x:c r="K18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="39" t="n">
+      <x:c r="L18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="39" t="n">
+      <x:c r="M18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2756,104 +2750,104 @@
       <x:c r="A19" s="2" t="str">
         <x:v>Missions</x:v>
       </x:c>
-      <x:c r="B19" s="40" t="n">
+      <x:c r="B19" s="38" t="n">
         <x:f>COUNTA('Missions'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C19" s="40" t="n">
+      <x:c r="C19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D19" s="40" t="n">
+      <x:c r="D19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E19" s="40" t="n">
+      <x:c r="E19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="40" t="n">
+      <x:c r="F19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="40" t="n">
+      <x:c r="G19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H19" s="40" t="n">
+      <x:c r="H19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I19" s="40" t="n">
+      <x:c r="I19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J19" s="40" t="n">
+      <x:c r="J19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="40" t="n">
+      <x:c r="K19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="40" t="n">
+      <x:c r="L19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M19" s="40" t="n">
+      <x:c r="M19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$E$7:$E$14,"P0")</x:f>
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="35" t="str">
+      <x:c r="A20" s="33" t="str">
         <x:v>Secondaires et DLC</x:v>
       </x:c>
-      <x:c r="B20" s="39" t="n">
+      <x:c r="B20" s="37" t="n">
         <x:f>COUNTA('Secondaires_DLC'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C20" s="39" t="n">
+      <x:c r="C20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D20" s="39" t="n">
+      <x:c r="D20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E20" s="39" t="n">
+      <x:c r="E20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F20" s="39" t="n">
+      <x:c r="F20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G20" s="39" t="n">
+      <x:c r="G20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H20" s="39" t="n">
+      <x:c r="H20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I20" s="39" t="n">
+      <x:c r="I20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J20" s="39" t="n">
+      <x:c r="J20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K20" s="39" t="n">
+      <x:c r="K20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L20" s="39" t="n">
+      <x:c r="L20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="39" t="n">
+      <x:c r="M20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2862,104 +2856,104 @@
       <x:c r="A21" s="2" t="str">
         <x:v>Choix et relations</x:v>
       </x:c>
-      <x:c r="B21" s="40" t="n">
+      <x:c r="B21" s="38" t="n">
         <x:f>COUNTA('Choix_relations'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C21" s="40" t="n">
+      <x:c r="C21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D21" s="40" t="n">
+      <x:c r="D21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E21" s="40" t="n">
+      <x:c r="E21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="40" t="n">
+      <x:c r="F21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G21" s="40" t="n">
+      <x:c r="G21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H21" s="40" t="n">
+      <x:c r="H21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I21" s="40" t="n">
+      <x:c r="I21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J21" s="40" t="n">
+      <x:c r="J21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K21" s="40" t="n">
+      <x:c r="K21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="40" t="n">
+      <x:c r="L21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M21" s="40" t="n">
+      <x:c r="M21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="35" t="str">
+      <x:c r="A22" s="33" t="str">
         <x:v>Dialogues</x:v>
       </x:c>
-      <x:c r="B22" s="39" t="n">
+      <x:c r="B22" s="37" t="n">
         <x:f>COUNTA('Dialogues'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C22" s="39" t="n">
+      <x:c r="C22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D22" s="39" t="n">
+      <x:c r="D22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E22" s="39" t="n">
+      <x:c r="E22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F22" s="39" t="n">
+      <x:c r="F22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G22" s="39" t="n">
+      <x:c r="G22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="39" t="n">
+      <x:c r="H22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I22" s="39" t="n">
+      <x:c r="I22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J22" s="39" t="n">
+      <x:c r="J22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="39" t="n">
+      <x:c r="K22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="39" t="n">
+      <x:c r="L22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="39" t="n">
+      <x:c r="M22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2968,104 +2962,104 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Cinématiques</x:v>
       </x:c>
-      <x:c r="B23" s="40" t="n">
+      <x:c r="B23" s="38" t="n">
         <x:f>COUNTA('Cinematiques'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C23" s="40" t="n">
+      <x:c r="C23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D23" s="40" t="n">
+      <x:c r="D23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="40" t="n">
+      <x:c r="E23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F23" s="40" t="n">
+      <x:c r="F23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="40" t="n">
+      <x:c r="G23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H23" s="40" t="n">
+      <x:c r="H23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I23" s="40" t="n">
+      <x:c r="I23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J23" s="40" t="n">
+      <x:c r="J23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K23" s="40" t="n">
+      <x:c r="K23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="40" t="n">
+      <x:c r="L23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M23" s="40" t="n">
+      <x:c r="M23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="35" t="str">
+      <x:c r="A24" s="33" t="str">
         <x:v>Armes</x:v>
       </x:c>
-      <x:c r="B24" s="39" t="n">
+      <x:c r="B24" s="37" t="n">
         <x:f>COUNTA('Armes'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C24" s="39" t="n">
+      <x:c r="C24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D24" s="39" t="n">
+      <x:c r="D24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E24" s="39" t="n">
+      <x:c r="E24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F24" s="39" t="n">
+      <x:c r="F24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="39" t="n">
+      <x:c r="G24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H24" s="39" t="n">
+      <x:c r="H24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I24" s="39" t="n">
+      <x:c r="I24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J24" s="39" t="n">
+      <x:c r="J24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="39" t="n">
+      <x:c r="K24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="39" t="n">
+      <x:c r="L24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="39" t="n">
+      <x:c r="M24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3074,104 +3068,104 @@
       <x:c r="A25" s="2" t="str">
         <x:v>Armures et équipement</x:v>
       </x:c>
-      <x:c r="B25" s="40" t="n">
+      <x:c r="B25" s="38" t="n">
         <x:f>COUNTA('Armures_equipement'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C25" s="40" t="n">
+      <x:c r="C25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D25" s="40" t="n">
+      <x:c r="D25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E25" s="40" t="n">
+      <x:c r="E25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F25" s="40" t="n">
+      <x:c r="F25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G25" s="40" t="n">
+      <x:c r="G25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H25" s="40" t="n">
+      <x:c r="H25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I25" s="40" t="n">
+      <x:c r="I25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J25" s="40" t="n">
+      <x:c r="J25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K25" s="40" t="n">
+      <x:c r="K25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="40" t="n">
+      <x:c r="L25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="40" t="n">
+      <x:c r="M25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="35" t="str">
+      <x:c r="A26" s="33" t="str">
         <x:v>Pouvoirs</x:v>
       </x:c>
-      <x:c r="B26" s="39" t="n">
+      <x:c r="B26" s="37" t="n">
         <x:f>COUNTA('Pouvoirs'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C26" s="39" t="n">
+      <x:c r="C26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D26" s="39" t="n">
+      <x:c r="D26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E26" s="39" t="n">
+      <x:c r="E26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F26" s="39" t="n">
+      <x:c r="F26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G26" s="39" t="n">
+      <x:c r="G26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H26" s="39" t="n">
+      <x:c r="H26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I26" s="39" t="n">
+      <x:c r="I26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J26" s="39" t="n">
+      <x:c r="J26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K26" s="39" t="n">
+      <x:c r="K26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="39" t="n">
+      <x:c r="L26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M26" s="39" t="n">
+      <x:c r="M26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3180,104 +3174,104 @@
       <x:c r="A27" s="2" t="str">
         <x:v>Movesets alliés</x:v>
       </x:c>
-      <x:c r="B27" s="40" t="n">
+      <x:c r="B27" s="38" t="n">
         <x:f>COUNTA('Movesets_allies'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C27" s="40" t="n">
+      <x:c r="C27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D27" s="40" t="n">
+      <x:c r="D27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E27" s="40" t="n">
+      <x:c r="E27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F27" s="40" t="n">
+      <x:c r="F27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="40" t="n">
+      <x:c r="G27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H27" s="40" t="n">
+      <x:c r="H27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I27" s="40" t="n">
+      <x:c r="I27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J27" s="40" t="n">
+      <x:c r="J27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="40" t="n">
+      <x:c r="K27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L27" s="40" t="n">
+      <x:c r="L27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="40" t="n">
+      <x:c r="M27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="35" t="str">
+      <x:c r="A28" s="33" t="str">
         <x:v>Movesets ennemis</x:v>
       </x:c>
-      <x:c r="B28" s="39" t="n">
+      <x:c r="B28" s="37" t="n">
         <x:f>COUNTA('Movesets_ennemis'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C28" s="39" t="n">
+      <x:c r="C28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D28" s="39" t="n">
+      <x:c r="D28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E28" s="39" t="n">
+      <x:c r="E28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F28" s="39" t="n">
+      <x:c r="F28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G28" s="39" t="n">
+      <x:c r="G28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="39" t="n">
+      <x:c r="H28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I28" s="39" t="n">
+      <x:c r="I28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J28" s="39" t="n">
+      <x:c r="J28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="39" t="n">
+      <x:c r="K28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="39" t="n">
+      <x:c r="L28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="39" t="n">
+      <x:c r="M28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3286,104 +3280,104 @@
       <x:c r="A29" s="2" t="str">
         <x:v>Animations</x:v>
       </x:c>
-      <x:c r="B29" s="40" t="n">
+      <x:c r="B29" s="38" t="n">
         <x:f>COUNTA('Animations'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C29" s="40" t="n">
+      <x:c r="C29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D29" s="40" t="n">
+      <x:c r="D29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E29" s="40" t="n">
+      <x:c r="E29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="40" t="n">
+      <x:c r="F29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="40" t="n">
+      <x:c r="G29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="40" t="n">
+      <x:c r="H29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I29" s="40" t="n">
+      <x:c r="I29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J29" s="40" t="n">
+      <x:c r="J29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="40" t="n">
+      <x:c r="K29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L29" s="40" t="n">
+      <x:c r="L29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="40" t="n">
+      <x:c r="M29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="35" t="str">
+      <x:c r="A30" s="33" t="str">
         <x:v>Sprites</x:v>
       </x:c>
-      <x:c r="B30" s="39" t="n">
+      <x:c r="B30" s="37" t="n">
         <x:f>COUNTA('Sprites'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C30" s="39" t="n">
+      <x:c r="C30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D30" s="39" t="n">
+      <x:c r="D30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E30" s="39" t="n">
+      <x:c r="E30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F30" s="39" t="n">
+      <x:c r="F30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G30" s="39" t="n">
+      <x:c r="G30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="39" t="n">
+      <x:c r="H30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I30" s="39" t="n">
+      <x:c r="I30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J30" s="39" t="n">
+      <x:c r="J30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K30" s="39" t="n">
+      <x:c r="K30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L30" s="39" t="n">
+      <x:c r="L30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M30" s="39" t="n">
+      <x:c r="M30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3392,104 +3386,104 @@
       <x:c r="A31" s="2" t="str">
         <x:v>VFX</x:v>
       </x:c>
-      <x:c r="B31" s="40" t="n">
+      <x:c r="B31" s="38" t="n">
         <x:f>COUNTA('VFX'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C31" s="40" t="n">
+      <x:c r="C31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D31" s="40" t="n">
+      <x:c r="D31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E31" s="40" t="n">
+      <x:c r="E31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F31" s="40" t="n">
+      <x:c r="F31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G31" s="40" t="n">
+      <x:c r="G31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H31" s="40" t="n">
+      <x:c r="H31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I31" s="40" t="n">
+      <x:c r="I31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J31" s="40" t="n">
+      <x:c r="J31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K31" s="40" t="n">
+      <x:c r="K31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L31" s="40" t="n">
+      <x:c r="L31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M31" s="40" t="n">
+      <x:c r="M31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="35" t="str">
+      <x:c r="A32" s="33" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="B32" s="39" t="n">
+      <x:c r="B32" s="37" t="n">
         <x:f>COUNTA('Audio'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C32" s="39" t="n">
+      <x:c r="C32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D32" s="39" t="n">
+      <x:c r="D32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E32" s="39" t="n">
+      <x:c r="E32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F32" s="39" t="n">
+      <x:c r="F32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="39" t="n">
+      <x:c r="G32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H32" s="39" t="n">
+      <x:c r="H32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I32" s="39" t="n">
+      <x:c r="I32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J32" s="39" t="n">
+      <x:c r="J32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="39" t="n">
+      <x:c r="K32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L32" s="39" t="n">
+      <x:c r="L32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" s="39" t="n">
+      <x:c r="M32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$E$7:$E$11,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3498,104 +3492,104 @@
       <x:c r="A33" s="2" t="str">
         <x:v>Systèmes et UI</x:v>
       </x:c>
-      <x:c r="B33" s="40" t="n">
+      <x:c r="B33" s="38" t="n">
         <x:f>COUNTA('UI_systemes'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C33" s="40" t="n">
+      <x:c r="C33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D33" s="40" t="n">
+      <x:c r="D33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E33" s="40" t="n">
+      <x:c r="E33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F33" s="40" t="n">
+      <x:c r="F33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G33" s="40" t="n">
+      <x:c r="G33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H33" s="40" t="n">
+      <x:c r="H33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I33" s="40" t="n">
+      <x:c r="I33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J33" s="40" t="n">
+      <x:c r="J33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="40" t="n">
+      <x:c r="K33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L33" s="40" t="n">
+      <x:c r="L33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M33" s="40" t="n">
+      <x:c r="M33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
-      <x:c r="A34" s="35" t="str">
+      <x:c r="A34" s="33" t="str">
         <x:v>QA</x:v>
       </x:c>
-      <x:c r="B34" s="39" t="n">
+      <x:c r="B34" s="37" t="n">
         <x:f>COUNTA('QA'!$A$7:$A$17)</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C34" s="39" t="n">
+      <x:c r="C34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$17,"Défini")</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D34" s="39" t="n">
+      <x:c r="D34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$17,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E34" s="39" t="n">
+      <x:c r="E34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$17,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F34" s="39" t="n">
+      <x:c r="F34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$17,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="39" t="n">
+      <x:c r="G34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$17,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="39" t="n">
+      <x:c r="H34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$17,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I34" s="39" t="n">
+      <x:c r="I34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$17,"Extrapolation")</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="J34" s="39" t="n">
+      <x:c r="J34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$17,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K34" s="39" t="n">
+      <x:c r="K34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$17,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L34" s="39" t="n">
+      <x:c r="L34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$17,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M34" s="39" t="n">
+      <x:c r="M34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$E$7:$E$17,"P0")</x:f>
         <x:v>11</x:v>
       </x:c>
@@ -3604,119 +3598,119 @@
       <x:c r="A35" s="2" t="str">
         <x:v>Continuité</x:v>
       </x:c>
-      <x:c r="B35" s="40" t="n">
+      <x:c r="B35" s="38" t="n">
         <x:f>COUNTA('Continuite'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C35" s="40" t="n">
+      <x:c r="C35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D35" s="40" t="n">
+      <x:c r="D35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E35" s="40" t="n">
+      <x:c r="E35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F35" s="40" t="n">
+      <x:c r="F35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G35" s="40" t="n">
+      <x:c r="G35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H35" s="40" t="n">
+      <x:c r="H35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I35" s="40" t="n">
+      <x:c r="I35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J35" s="40" t="n">
+      <x:c r="J35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K35" s="40" t="n">
+      <x:c r="K35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L35" s="40" t="n">
+      <x:c r="L35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M35" s="40" t="n">
+      <x:c r="M35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="2"/>
-      <x:c r="B36" s="40"/>
-      <x:c r="C36" s="40"/>
-      <x:c r="D36" s="40"/>
-      <x:c r="E36" s="40"/>
-      <x:c r="F36" s="40"/>
-      <x:c r="G36" s="40"/>
-      <x:c r="H36" s="40"/>
-      <x:c r="I36" s="40"/>
-      <x:c r="J36" s="40"/>
-      <x:c r="K36" s="40"/>
-      <x:c r="L36" s="40"/>
-      <x:c r="M36" s="40"/>
+      <x:c r="B36" s="38"/>
+      <x:c r="C36" s="38"/>
+      <x:c r="D36" s="38"/>
+      <x:c r="E36" s="38"/>
+      <x:c r="F36" s="38"/>
+      <x:c r="G36" s="38"/>
+      <x:c r="H36" s="38"/>
+      <x:c r="I36" s="38"/>
+      <x:c r="J36" s="38"/>
+      <x:c r="K36" s="38"/>
+      <x:c r="L36" s="38"/>
+      <x:c r="M36" s="38"/>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="23" t="str">
+      <x:c r="A37" s="21" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B37" s="41" t="n">
+      <x:c r="B37" s="39" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>160</x:v>
       </x:c>
-      <x:c r="C37" s="41" t="n">
+      <x:c r="C37" s="39" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="D37" s="41" t="n">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D37" s="39" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E37" s="41" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E37" s="39" t="n">
         <x:f>SUM(E10:E35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F37" s="41" t="n">
+      <x:c r="F37" s="39" t="n">
         <x:f>SUM(F10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G37" s="41" t="n">
+      <x:c r="G37" s="39" t="n">
         <x:f>SUM(G10:G35)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H37" s="41" t="n">
+      <x:c r="H37" s="39" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>28</x:v>
       </x:c>
-      <x:c r="I37" s="41" t="n">
+      <x:c r="I37" s="39" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>129</x:v>
       </x:c>
-      <x:c r="J37" s="41" t="n">
+      <x:c r="J37" s="39" t="n">
         <x:f>SUM(J10:J35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K37" s="41" t="n">
+      <x:c r="K37" s="39" t="n">
         <x:f>SUM(K10:K35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L37" s="41" t="n">
+      <x:c r="L37" s="39" t="n">
         <x:f>SUM(L10:L35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M37" s="41" t="n">
+      <x:c r="M37" s="39" t="n">
         <x:f>SUM(M10:M35)</x:f>
         <x:v>23</x:v>
       </x:c>
@@ -3940,61 +3934,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4048,10 +4042,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>DIS-S-ISSUE2</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_2</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4105,10 +4099,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>DIS-S-ISSUE4</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_4</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4162,10 +4156,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>DIS-S-OPENING</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_IV</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4219,10 +4213,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>DIS-S-ISSUE3</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_3</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4258,7 +4252,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3db059d7e06045cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66e094f7fde949d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4398,61 +4392,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4506,8 +4500,8 @@
         <x:v>Conception originale rattachée à Discovery #1</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -4559,8 +4553,8 @@
         <x:v>Conception originale rattachée à Discovery #1</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -4612,8 +4606,8 @@
         <x:v>Conception originale rattachée à Discovery #2</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -4665,8 +4659,8 @@
         <x:v>Conception originale rattachée à Discovery #2</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -4718,8 +4712,8 @@
         <x:v>Conception originale rattachée à Discovery #3</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -4771,8 +4765,8 @@
         <x:v>Conception originale rattachée à Discovery #3</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -4824,8 +4818,8 @@
         <x:v>Conception originale rattachée à Discovery #4</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -4877,8 +4871,8 @@
         <x:v>Conception originale rattachée à Discovery #4</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -4912,7 +4906,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd3c82b728804b04"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb751253747a49d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5052,61 +5046,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5160,8 +5154,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5213,8 +5207,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5266,8 +5260,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5319,8 +5313,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5372,8 +5366,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -5425,8 +5419,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -5478,8 +5472,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -5531,8 +5525,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -5566,7 +5560,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7ef9ee6e4b24a50"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1079cc071ccd47fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5706,61 +5700,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5814,8 +5808,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5867,8 +5861,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5920,8 +5914,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5973,8 +5967,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -6026,8 +6020,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -6079,8 +6073,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -6132,8 +6126,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -6185,8 +6179,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -6220,7 +6214,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa4e42a55e4e4e89"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59795c8d56474989"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6360,61 +6354,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6468,8 +6462,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -6521,8 +6515,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -6574,8 +6568,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -6627,8 +6621,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -6680,8 +6674,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -6733,8 +6727,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -6786,8 +6780,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -6839,8 +6833,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -6874,7 +6868,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra68e15d3913f42c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17509602a83f45d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7014,61 +7008,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7120,8 +7114,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -7171,8 +7165,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -7222,8 +7216,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -7273,8 +7267,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -7324,8 +7318,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -7375,8 +7369,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -7426,8 +7420,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -7477,8 +7471,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -7512,7 +7506,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5484ca11081b4898"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d9aa3676f0c4617"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7652,61 +7646,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7760,10 +7754,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>DIS-S-ISSUE3</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_3</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -7813,8 +7807,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -7848,7 +7842,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e6051be90694a07"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reae04e3add3645dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7988,61 +7982,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8094,8 +8088,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8145,8 +8139,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -8180,7 +8174,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99f8f4030c4e4e01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8252edfc6c474c70"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8320,61 +8314,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8426,8 +8420,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -8461,7 +8455,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e9eb6490c80499e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31afe2646f3b4e34"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8601,61 +8595,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8709,8 +8703,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8762,8 +8756,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -8815,8 +8809,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -8850,7 +8844,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84d17b97187048e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62eb95c6d2624f22"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8990,61 +8984,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9098,10 +9092,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>DIS-S-COMPLETE</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://digital.darkhorse.com/books/7bcdbde713b746338287bb0d74350bac/mass-effect-the-complete-comics</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -9155,10 +9149,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>DIS-S-OPENING</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_IV</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -9212,10 +9206,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>DIS-S-OPENING</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_IV</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -9269,10 +9263,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>DIS-S-ISSUE2</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_2</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -9308,7 +9302,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e767cf5de4d4b92"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R311964a0b82044f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9448,61 +9442,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9556,8 +9550,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9609,8 +9603,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -9662,8 +9656,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -9715,8 +9709,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -9768,8 +9762,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -9821,8 +9815,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -9874,8 +9868,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -9927,8 +9921,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -9962,7 +9956,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba0887a95621409a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd02179379d274101"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10102,61 +10096,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10208,8 +10202,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10259,8 +10253,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10310,8 +10304,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10361,8 +10355,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10412,8 +10406,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -10463,8 +10457,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -10514,8 +10508,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -10565,8 +10559,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -10616,8 +10610,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -10667,8 +10661,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D16">
@@ -10702,7 +10696,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1095329e6d74f40"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27843e4e7882415a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10842,61 +10836,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10946,8 +10940,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10995,8 +10989,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11044,8 +11038,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11093,8 +11087,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -11142,8 +11136,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -11191,8 +11185,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -11240,8 +11234,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -11289,8 +11283,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -11338,8 +11332,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -11387,8 +11381,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D16">
@@ -11422,7 +11416,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d3caa6746884441"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d8301c7f1824c0a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11562,61 +11556,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11668,8 +11662,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11719,8 +11713,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11770,8 +11764,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11821,8 +11815,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -11872,8 +11866,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -11923,8 +11917,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -11974,8 +11968,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -12025,8 +12019,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -12060,7 +12054,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3838b9e4a74e4e32"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ff6b306a1944144"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12200,61 +12194,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12308,8 +12302,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12361,8 +12355,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12414,8 +12408,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12467,8 +12461,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12520,8 +12514,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D11">
@@ -12555,7 +12549,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a4af7ff9bc1415c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58d2471d6b6a4a48"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12695,61 +12689,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12797,8 +12791,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12844,8 +12838,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12891,8 +12885,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12938,8 +12932,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -12973,7 +12967,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R071386e1d332430d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re00869207b4c4b3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13113,61 +13107,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13215,8 +13209,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -13262,8 +13256,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -13309,8 +13303,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -13356,8 +13350,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -13403,8 +13397,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -13450,8 +13444,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -13497,8 +13491,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -13544,8 +13538,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -13589,8 +13583,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -13634,8 +13628,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="82" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -13679,8 +13673,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D17">
@@ -13714,7 +13708,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f90f3e70d434907"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc96f8fb649b4c6f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13854,61 +13848,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13954,8 +13948,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -13999,8 +13993,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -14034,7 +14028,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R885ae99db87d45d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4880bc2484f64e62"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14099,10 +14093,10 @@
       <x:c r="F5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Champ</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="B6" s="30" t="str">
         <x:v>Définition</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
@@ -14146,12 +14140,12 @@
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
     </x:row>
-    <x:row r="10" ht="68" customHeight="1">
+    <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="7" t="str">
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Adaptation d’enquête en duo autour de Tiran Kandros, fondée sur une couverture, une poursuite et une décision d’engagement. Les calculs astrométriques sont des objectifs abstraits, pas des données scientifiques inventées.</x:v>
+        <x:v>160 fiches de production ; 2 fiches au stade Prototype de portée partielle. Les autres livrables restent des spécifications ; aucun achèvement intégral 1:1 revendiqué.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -14170,11 +14164,11 @@
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="d">
+      <x:c r="B12" s="42" t="d">
         <x:v>2026-10-22T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
@@ -14327,22 +14321,22 @@
       <x:c r="F25" s="2"/>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="30" t="str">
+      <x:c r="A26" s="28" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="str">
+      <x:c r="B26" s="29" t="str">
         <x:v>Titre</x:v>
       </x:c>
-      <x:c r="C26" s="31" t="str">
+      <x:c r="C26" s="29" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="str">
+      <x:c r="D26" s="29" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="E26" s="31" t="str">
+      <x:c r="E26" s="29" t="str">
         <x:v>Périmètre</x:v>
       </x:c>
-      <x:c r="F26" s="32" t="str">
+      <x:c r="F26" s="30" t="str">
         <x:v>Accès et limites</x:v>
       </x:c>
     </x:row>
@@ -14491,13 +14485,13 @@
       <x:c r="F35" s="2"/>
     </x:row>
     <x:row r="36" ht="34" customHeight="1">
-      <x:c r="A36" s="30" t="str">
+      <x:c r="A36" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B36" s="31" t="str">
+      <x:c r="B36" s="29" t="str">
         <x:v>Couverture actuelle</x:v>
       </x:c>
-      <x:c r="C36" s="32" t="str">
+      <x:c r="C36" s="30" t="str">
         <x:v>Travail restant</x:v>
       </x:c>
       <x:c r="D36" s="2"/>
@@ -14868,10 +14862,16 @@
       <x:c r="E62" s="2"/>
       <x:c r="F62" s="2"/>
     </x:row>
-    <x:row r="63" ht="22" customHeight="1">
-      <x:c r="A63" s="2"/>
-      <x:c r="B63" s="2"/>
-      <x:c r="C63" s="2"/>
+    <x:row r="63" ht="96" customHeight="1">
+      <x:c r="A63" s="6" t="str">
+        <x:v>Complément lectures contextualisées</x:v>
+      </x:c>
+      <x:c r="B63" s="6" t="str">
+        <x:v>2 références supplémentaires au stade Prototype dans 1 parcours de lecture (1 pages de paraphrases documentaires sourcées), limités à leurs segments exacts.</x:v>
+      </x:c>
+      <x:c r="C63" s="6" t="str">
+        <x:v>Les faits, références, sources et réserves d’origine sont conservés. Ces lectures ne constituent ni un découpage intégral, ni une scène jouable, ni un recrutement ; modèles, voix et animations de l’œuvre ne sont pas produits.</x:v>
+      </x:c>
       <x:c r="D63" s="2"/>
       <x:c r="E63" s="2"/>
       <x:c r="F63" s="2"/>
@@ -15427,6 +15427,14 @@
       <x:c r="D132" s="2"/>
       <x:c r="E132" s="2"/>
       <x:c r="F132" s="2"/>
+    </x:row>
+    <x:row r="133" ht="22" customHeight="1">
+      <x:c r="A133" s="2"/>
+      <x:c r="B133" s="2"/>
+      <x:c r="C133" s="2"/>
+      <x:c r="D133" s="2"/>
+      <x:c r="E133" s="2"/>
+      <x:c r="F133" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15568,61 +15576,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -15676,10 +15684,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>DIS-S-OPENING</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_IV</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -15733,10 +15741,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>DIS-S-OPENING</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_IV</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -15790,10 +15798,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>DIS-S-ISSUE3</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_3</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -15847,10 +15855,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>DIS-S-ISSUE2</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_2</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -15904,10 +15912,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>DIS-S-ISSUE2</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_2</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -15961,10 +15969,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>DIS-S-ISSUE3</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_3</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -16000,7 +16008,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd46becb5203e4882"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79b1c354170a4842"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16027,7 +16035,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="158" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -16140,65 +16148,65 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="54" customHeight="1">
+    <x:row r="7" ht="82" customHeight="1">
       <x:c r="A7" s="18" t="str">
         <x:v>DIS-REF-SCOPE</x:v>
       </x:c>
@@ -16206,7 +16214,7 @@
         <x:v>Infiltration de l’Initiative</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16225,7 +16233,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>Livrable proposé : spécification DIS/lore/ref-scope; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Référence documentaire DIS-REF-SCOPE consultable dans les lectures dis-infiltration de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ni incarnation de personnage produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>Vérifier toute précision non contenue dans cette notice avant de la déclarer canon.</x:v>
@@ -16240,14 +16248,14 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>DIS-S-BOOK</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/539581/mass-effect-discovery-by-based-off-game-by-bioware-written-by-jeremy-barlow-illustrated-by-gabriel-guzman-and-michael-atiyeh/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
-        <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="54" customHeight="1">
+      <x:c r="S7" s="9" t="str">
+        <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit. Prototype limité à une paraphrase documentaire sourcée et aux références visitées ; pas de reproduction intégrale du récit. Une lecture n’accorde ni recrutement, équipement, victoire ni récompense de campagne.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
         <x:v>DIS-REF-TIRAN</x:v>
       </x:c>
@@ -16255,7 +16263,7 @@
         <x:v>Tiran Kandros</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
         <x:v>Établi</x:v>
@@ -16274,7 +16282,7 @@
       <x:c r="J8" s="7" t="str"/>
       <x:c r="K8" s="7" t="str"/>
       <x:c r="L8" s="7" t="str">
-        <x:v>Livrable proposé : spécification DIS/lore/ref-tiran; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Référence documentaire DIS-REF-TIRAN consultable dans les lectures dis-infiltration de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ni incarnation de personnage produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M8" s="7" t="str">
         <x:v>Vérifier toute précision non contenue dans cette notice avant de la déclarer canon.</x:v>
@@ -16289,11 +16297,11 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>DIS-S-COMPLETE</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://digital.darkhorse.com/books/7bcdbde713b746338287bb0d74350bac/mass-effect-the-complete-comics</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
-        <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
+      <x:c r="S8" s="7" t="str">
+        <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit. Prototype limité à une paraphrase documentaire sourcée et aux références visitées ; pas de reproduction intégrale du récit. Une lecture n’accorde ni recrutement, équipement, victoire ni récompense de campagne.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
@@ -16338,10 +16346,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>DIS-S-ISSUE2</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_2</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -16387,10 +16395,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>DIS-S-ISSUE4</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_4</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -16436,10 +16444,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>DIS-S-OPENING</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_IV</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -16485,10 +16493,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>DIS-S-OPENING</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_IV</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -16534,10 +16542,10 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>DIS-S-ISSUE2</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_2</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="S13" s="9" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -16583,10 +16591,10 @@
       <x:c r="Q14" s="7" t="str">
         <x:v>DIS-S-ISSUE2</x:v>
       </x:c>
-      <x:c r="R14" s="21" t="str">
+      <x:c r="R14" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_2</x:v>
       </x:c>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="S14" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -16632,10 +16640,10 @@
       <x:c r="Q15" s="9" t="str">
         <x:v>DIS-S-ISSUE3</x:v>
       </x:c>
-      <x:c r="R15" s="20" t="str">
+      <x:c r="R15" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_3</x:v>
       </x:c>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="S15" s="9" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -16681,10 +16689,10 @@
       <x:c r="Q16" s="7" t="str">
         <x:v>DIS-S-ISSUE3</x:v>
       </x:c>
-      <x:c r="R16" s="21" t="str">
+      <x:c r="R16" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_3</x:v>
       </x:c>
-      <x:c r="S16" s="21" t="str">
+      <x:c r="S16" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -16730,10 +16738,10 @@
       <x:c r="Q17" s="9" t="str">
         <x:v>DIS-S-ISSUE4</x:v>
       </x:c>
-      <x:c r="R17" s="20" t="str">
+      <x:c r="R17" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_4</x:v>
       </x:c>
-      <x:c r="S17" s="20" t="str">
+      <x:c r="S17" s="9" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -16779,10 +16787,10 @@
       <x:c r="Q18" s="7" t="str">
         <x:v>DIS-S-ISSUE4</x:v>
       </x:c>
-      <x:c r="R18" s="21" t="str">
+      <x:c r="R18" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_4</x:v>
       </x:c>
-      <x:c r="S18" s="21" t="str">
+      <x:c r="S18" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -16818,7 +16826,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1969680b116746e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d9bea521c7840b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16958,61 +16966,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -17060,10 +17068,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>DIS-S-OPENING</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_IV</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -17111,10 +17119,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>DIS-S-OPENING</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_IV</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -17162,10 +17170,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>DIS-S-ISSUE2</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_2</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -17213,10 +17221,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>DIS-S-ISSUE3</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_3</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -17264,10 +17272,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>DIS-S-ISSUE4</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Discovery_4</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -17303,7 +17311,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R510da6a926a64e5a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc367c33b79214c7b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17443,61 +17451,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -17549,8 +17557,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -17600,8 +17608,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -17651,8 +17659,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -17702,8 +17710,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -17753,8 +17761,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D11">
@@ -17788,7 +17796,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e20cefa337b4676"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe6a542f8a76435f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17928,61 +17936,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18032,8 +18040,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -18081,8 +18089,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -18130,8 +18138,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -18179,8 +18187,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -18228,8 +18236,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D11">
@@ -18263,7 +18271,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a49e57741354def"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R601b81c52239499e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18403,61 +18411,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18507,8 +18515,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -18556,8 +18564,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -18605,8 +18613,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -18654,8 +18662,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -18703,8 +18711,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D11">
@@ -18738,7 +18746,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbb2d22b4c83479e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f3fbaecfa564bfc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18878,61 +18886,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18986,8 +18994,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -19039,8 +19047,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -19092,8 +19100,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -19145,8 +19153,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -19198,8 +19206,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -19251,8 +19259,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -19304,8 +19312,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -19357,8 +19365,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -19392,7 +19400,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b5a11b835934073"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cf6844b114a4fb3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Discovery_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Discovery_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R4d96954f106f4215"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rba153eaaf9114c5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R4cd9d9d31a3145f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R4c9765fe883e4fe3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R8af493cf5b8340a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rd5d7885b06184a4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R2b0665e4f2274bad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rd2118e4ac0994560"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R4b5d9de797214e9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rbdbb0a596ea5452e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rb19ed8969c354ca3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rb7482e2d3e314d2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R94a1f50db488411b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R0c3caf3c0c3d4cea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rfe381aaa73a443ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Re33e27b4facf4893"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R7385e9f07ddc4891"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R23cef640e0e04f29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R1f5bc07683864681"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rff3920a5da24468e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R7d61fa068b7c4d37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R70558b526798494a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R973d95f36cfb4bd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rbb1c7dfc18a6447a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rb6b6094458494ee4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R877a782825204dbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Ra53447bf3ca2446d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R1c8e0392ed804be7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rf85d7356304e4111"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rb93c4790c4df44d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R6cef778c6dc8479a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rf9286253c82241d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rbd5a36f88c94444c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R3c51697d3630452a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R121444158f4c445e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R772e983dfe7a4ab2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rf33c53f7c0994d65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R6cfab149f1be49a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rf592f960e5104d76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Recbb04e6ce1742ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Re35f42946c594bb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R96dc024788c94fca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R9614434ddc0b4073"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rd960f12373b141fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Ra0987ffc98fb45a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R7615b5b902704493"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R8cf6775786544849"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rf1e5d22126274ea3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Reedee1238bd245a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R1fb367e92de44ab1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R6d398387e0364991"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R0923498e8bc94cdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R9935d3e95e3548ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R826dcb7a54cf48a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R4a272fb9fa5a4d48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Radd8a8aac05844da"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4252,7 +4252,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66e094f7fde949d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c2805dab0fb48d4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4906,7 +4906,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb751253747a49d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29122de2e7204e77"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5560,7 +5560,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1079cc071ccd47fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18629bdd7d014c8c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6214,7 +6214,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59795c8d56474989"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R467c8290e45d4efc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6868,7 +6868,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17509602a83f45d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb028a579a5e5448c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7506,7 +7506,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d9aa3676f0c4617"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15d31b3d7f6345e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7842,7 +7842,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reae04e3add3645dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf63a882699924d23"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8174,7 +8174,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8252edfc6c474c70"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf02efb6dc55423d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8455,7 +8455,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31afe2646f3b4e34"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0eb9cb171cca40cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8844,7 +8844,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62eb95c6d2624f22"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6079972beba449b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9302,7 +9302,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R311964a0b82044f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R498023abe339423f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9956,7 +9956,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd02179379d274101"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref8c755ea4b54687"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10696,7 +10696,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27843e4e7882415a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d7e604e47cf485b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11416,7 +11416,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d8301c7f1824c0a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7135108352da435c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12054,7 +12054,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ff6b306a1944144"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R612cb09aa11e4e11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12549,7 +12549,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58d2471d6b6a4a48"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra52e87f516834a86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12967,7 +12967,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re00869207b4c4b3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08c134abd0bb4c54"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13708,7 +13708,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc96f8fb649b4c6f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf450310d2b674f96"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14028,7 +14028,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4880bc2484f64e62"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd500814a2c7541aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16008,7 +16008,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79b1c354170a4842"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra67972fc072f4966"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16826,7 +16826,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d9bea521c7840b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c958a8f4de145e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17311,7 +17311,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc367c33b79214c7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04db2e0e6a5546f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17796,7 +17796,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe6a542f8a76435f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c864d5c55d74f54"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18271,7 +18271,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R601b81c52239499e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra13b661e74b948c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18746,7 +18746,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f3fbaecfa564bfc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8486e37833f4324"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19400,7 +19400,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cf6844b114a4fb3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51acb6f120fb4aac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Discovery_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Discovery_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rf85d7356304e4111"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rb93c4790c4df44d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R6cef778c6dc8479a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rf9286253c82241d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rbd5a36f88c94444c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R3c51697d3630452a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R121444158f4c445e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R772e983dfe7a4ab2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rf33c53f7c0994d65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R6cfab149f1be49a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rf592f960e5104d76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Recbb04e6ce1742ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Re35f42946c594bb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R96dc024788c94fca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R9614434ddc0b4073"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rd960f12373b141fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Ra0987ffc98fb45a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R7615b5b902704493"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R8cf6775786544849"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rf1e5d22126274ea3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Reedee1238bd245a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R1fb367e92de44ab1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R6d398387e0364991"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R0923498e8bc94cdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R9935d3e95e3548ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R826dcb7a54cf48a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R4a272fb9fa5a4d48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Radd8a8aac05844da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R6c6409824f6a408d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rde48772ea7044079"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R4ff7f8e7d3084d4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R939bf74939b04ebc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R974b722daab34366"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rc042b7f79c5b48e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R90a7ac8275e64359"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R99fe7f964e884c4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Re2c0ac7ad8cf474a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R9454494bd2ae4d59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R53ef52da46054881"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Re7078c43aca4402d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R2f07d5d8334d4c1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rbedeb48f0cc84e08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R0616f880dccc47d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R5751e56cb21d4784"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R2db457c10acf4a84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rb1834167ed614471"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R8e5bad76dbe7440b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R4e2424c222b440e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R3084e008b9b24feb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R70fcf912ea7849a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R85b60b80554f450f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R14650c25c50a4b67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R7c62d554ec32462c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rc7e5054e072b4e76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R058bef3d79ed4607"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R3512e7a9a063490b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4252,7 +4252,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c2805dab0fb48d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R292851982b6547a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4906,7 +4906,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29122de2e7204e77"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fa93fc12a1a4cb6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5560,7 +5560,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18629bdd7d014c8c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ce2399f87b34a62"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6214,7 +6214,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R467c8290e45d4efc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7bcd3c02a324e0f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6868,7 +6868,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb028a579a5e5448c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69f44d1c7970444e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7506,7 +7506,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15d31b3d7f6345e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb977014407fe47bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7842,7 +7842,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf63a882699924d23"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7eca0501da34cb8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8174,7 +8174,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf02efb6dc55423d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4c4202b7f7849b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8455,7 +8455,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0eb9cb171cca40cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R372b67a921d34736"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8844,7 +8844,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6079972beba449b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35b03b4ec1624202"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9302,7 +9302,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R498023abe339423f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra06248353b7e4035"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9956,7 +9956,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref8c755ea4b54687"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf3712a614354693"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10696,7 +10696,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d7e604e47cf485b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R300fa57b1ed24529"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11416,7 +11416,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7135108352da435c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb415b0a93584d86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12054,7 +12054,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R612cb09aa11e4e11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07d3577047074d0b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12549,7 +12549,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra52e87f516834a86"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R163ffcc69c664945"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12967,7 +12967,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08c134abd0bb4c54"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a596e5c3e5b48c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13708,7 +13708,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf450310d2b674f96"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf9ae52feb30437c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14028,7 +14028,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd500814a2c7541aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c3b05c1aa584212"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16008,7 +16008,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra67972fc072f4966"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61031798efc54f51"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16826,7 +16826,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c958a8f4de145e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R779ebd48ef6c4fdd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17311,7 +17311,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04db2e0e6a5546f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa912ddb482e4db8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17796,7 +17796,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c864d5c55d74f54"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4841dd1fc9eb4df2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18271,7 +18271,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra13b661e74b948c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15b73c082b8e4829"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18746,7 +18746,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8486e37833f4324"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5d1ae98347e43e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19400,7 +19400,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51acb6f120fb4aac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ba775fe4b94427c"/>
   </x:tableParts>
 </x:worksheet>
 </file>